--- a/reports/out/report.xlsx
+++ b/reports/out/report.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tsn_perclass" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tsm_perclass" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i3d_perclass" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r2plus1d_perclass" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="videomae_perclass" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="tsn_perclass" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="tsm_perclass" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="i3d_perclass" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="r2plus1d_perclass" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="videomae_perclass" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -604,32 +604,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tsn</t>
+          <t>tsm</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.523121387283237</v>
+        <v>0.5144508670520231</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5522798504777404</v>
+        <v>0.5536007143749206</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5355227628685884</v>
+        <v>0.5200438239812054</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5348746586771476</v>
+        <v>0.5205463528632277</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1007103286500068</v>
+        <v>0.1092853713999829</v>
       </c>
       <c r="G5" t="n">
-        <v>79.43574514389645</v>
+        <v>73.20284405421572</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>0.8625</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2949991618536111</v>
+        <v>0.2653738605235353</v>
       </c>
       <c r="J5" t="n">
         <v>11181642</v>
@@ -641,32 +641,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tsm</t>
+          <t>tsn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5144508670520231</v>
+        <v>0.1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5536007143749206</v>
+        <v>0.01</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5200438239812054</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5205463528632277</v>
+        <v>0.0181818181818181</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1092853713999829</v>
+        <v>0.0826401558002544</v>
       </c>
       <c r="G6" t="n">
-        <v>73.20284405421572</v>
+        <v>96.80523859776372</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8625</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2653738605235353</v>
+        <v>0.1781979948282241</v>
       </c>
       <c r="J6" t="n">
         <v>11181642</v>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7761194029850746</v>
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="3">
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4516129032258064</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5384615384615384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3666666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.725</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9354838709677419</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8169014084507042</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5294117647058824</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5806451612903226</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5538461538461539</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8260869565217391</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6129032258064516</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7037037037037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2727272727272727</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2696629213483146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.71875</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6764705882352942</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.696969696969697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3285714285714286</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5111111111111111</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2727272727272727</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1935483870967742</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2264150943396226</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
